--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -603,10 +603,22 @@
       <c r="O2" t="n">
         <v>10000</v>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>20300</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>103.00%</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>16560</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-18.42%</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -603,10 +603,22 @@
       <c r="O2" t="n">
         <v>10000</v>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>16560</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>65.60%</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>9400</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-43.24%</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,6 +693,67 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>에이치엘지노믹스</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>기초 의약물질 제조업</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>및</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>21500</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -664,13 +664,21 @@
           <t>17.93%</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>77.50%</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>41.03%</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>31.89%</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>1579억</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,6 +701,67 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>에이치엘지노믹스</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>기초 의약물질 제조업</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>및</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>21500</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,6 +701,73 @@
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>에이치엘지노믹스</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>기초 의약물질 제조업</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>KB증권, IBK투자증권</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>714.52</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1673억</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>21500</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -692,10 +692,22 @@
       <c r="O3" t="n">
         <v>20700</v>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>30750</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>48.55%</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>22000</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>-28.46%</t>
+        </is>
+      </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -745,19 +745,29 @@
       <c r="G4" t="n">
         <v>714.52</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>667.1799999999999</v>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1.91%</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>34.58%</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>33.00%</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>24.41%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>1673억</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -781,10 +781,22 @@
       <c r="O4" t="n">
         <v>21500</v>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>21500</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>14790</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-31.21%</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W4"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,6 +802,63 @@
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>인제니아테라퓨틱스</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>자연과학 및 공학 연구개발업</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>삼성증권</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>12000</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -831,7 +831,9 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>50.4</v>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
@@ -839,9 +841,17 @@
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>25.60%</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5933억</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>무</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W5"/>
+  <dimension ref="A1:W6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,6 +869,73 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>딜리셔스</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>무점포 소매업</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>한국투자증권</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>184.06</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.10%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>36.93%</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1532억</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>유</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>7000</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -936,6 +936,73 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>케이앤에스아이앤씨</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>통신 및 방송 장비 제조업</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>IBK투자증권</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>938.24</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>55.44%</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>11000</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -977,7 +977,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>55.44%</t>
+          <t>30.00%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -901,7 +901,9 @@
       <c r="G6" t="n">
         <v>184.06</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>10.29</v>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>0.10%</t>
@@ -962,7 +964,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1005,6 +1005,75 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>케이앤에스아이앤씨</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>통신 및 방송 장비 제조업</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>IBK투자증권</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>938.24</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1079.55</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>30.00%</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>11000</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,79 +546,67 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>딜리셔스</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>무점포 소매업</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1238</v>
+        <v>184.06</v>
       </c>
       <c r="H2" t="n">
-        <v>1510.57</v>
+        <v>10.29</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>74.17%</t>
+          <t>6.24%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>33.19%</t>
+          <t>36.93%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>24.86%</t>
+          <t>36.42%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1335억</t>
+          <t>1532억</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>16560</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>65.60%</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>9400</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>-43.24%</t>
-        </is>
-      </c>
+        <v>7000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -724,53 +712,53 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>714.52</v>
+        <v>1238</v>
       </c>
       <c r="H4" t="n">
-        <v>667.1799999999999</v>
+        <v>1510.57</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>6.92%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>34.58%</t>
+          <t>74.17%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>33.00%</t>
+          <t>33.19%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>24.41%</t>
+          <t>24.86%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1673억</t>
+          <t>1335억</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -779,22 +767,22 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>21500</v>
+        <v>10000</v>
       </c>
       <c r="P4" t="n">
-        <v>21500</v>
+        <v>16560</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>65.60%</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>14790</v>
+        <v>9400</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-31.21%</t>
+          <t>-43.24%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -813,43 +801,53 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>714.52</v>
+      </c>
+      <c r="H5" t="n">
+        <v>667.1799999999999</v>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>34.58%</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>25.60%</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>24.41%</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>5933억</t>
+          <t>1673억</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -858,12 +856,24 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+        <v>21500</v>
+      </c>
+      <c r="P5" t="n">
+        <v>21500</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>14790</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-31.21%</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
@@ -880,54 +890,52 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>무점포 소매업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>184.06</v>
-      </c>
-      <c r="H6" t="n">
-        <v>10.29</v>
-      </c>
+        <v>50.4</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>36.93%</t>
+          <t>25.60%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1532억</t>
+          <t>5933억</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
@@ -970,7 +978,9 @@
       <c r="G7" t="n">
         <v>938.24</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>1079.55</v>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>0.78%</t>
@@ -1005,75 +1015,6 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>케이앤에스아이앤씨</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>통신 및 방송 장비 제조업</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>IBK투자증권</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>938.24</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>30.00%</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>11000</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -986,13 +986,21 @@
           <t>0.78%</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>30.00%</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>1129억</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,53 +546,43 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>기도산업</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>무점포 소매업</t>
+          <t>봉제의복 제조업</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>184.06</v>
-      </c>
-      <c r="H2" t="n">
-        <v>10.29</v>
-      </c>
+        <v>213.31</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.10%</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>6.24%</t>
-        </is>
-      </c>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>36.93%</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>36.42%</t>
-        </is>
-      </c>
+          <t>66.92%</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1532억</t>
+          <t>1660억</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -601,7 +591,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>7000</v>
+        <v>28400</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -623,79 +613,67 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>딜리셔스</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>무점포 소매업</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1146.41</v>
+        <v>184.06</v>
       </c>
       <c r="H3" t="n">
-        <v>1706.71</v>
+        <v>10.29</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>17.93%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.50%</t>
+          <t>6.24%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>41.03%</t>
+          <t>36.93%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>31.89%</t>
+          <t>36.42%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1579억</t>
+          <t>1532억</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>20700</v>
-      </c>
-      <c r="P3" t="n">
-        <v>30750</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>48.55%</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>22000</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>-28.46%</t>
-        </is>
-      </c>
+        <v>7000</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
@@ -712,12 +690,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -727,38 +705,38 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1238</v>
+        <v>1146.41</v>
       </c>
       <c r="H4" t="n">
-        <v>1510.57</v>
+        <v>1706.71</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>17.93%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>74.17%</t>
+          <t>77.50%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>33.19%</t>
+          <t>41.03%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>24.86%</t>
+          <t>31.89%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1335억</t>
+          <t>1579억</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -767,22 +745,22 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>10000</v>
+        <v>20700</v>
       </c>
       <c r="P4" t="n">
-        <v>16560</v>
+        <v>30750</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>65.60%</t>
+          <t>48.55%</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>9400</v>
+        <v>22000</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-43.24%</t>
+          <t>-28.46%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -801,53 +779,53 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>714.52</v>
+        <v>1238</v>
       </c>
       <c r="H5" t="n">
-        <v>667.1799999999999</v>
+        <v>1510.57</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>6.92%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>34.58%</t>
+          <t>74.17%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>33.00%</t>
+          <t>33.19%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>24.41%</t>
+          <t>24.86%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1673억</t>
+          <t>1335억</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -856,22 +834,22 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>21500</v>
+        <v>10000</v>
       </c>
       <c r="P5" t="n">
-        <v>21500</v>
+        <v>16560</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>65.60%</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>14790</v>
+        <v>9400</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.21%</t>
+          <t>-43.24%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -890,43 +868,53 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>714.52</v>
+      </c>
+      <c r="H6" t="n">
+        <v>667.1799999999999</v>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>34.58%</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>25.60%</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>24.41%</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>5933억</t>
+          <t>1673억</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -935,12 +923,24 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+        <v>21500</v>
+      </c>
+      <c r="P6" t="n">
+        <v>21500</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>14790</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>-31.21%</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
@@ -957,53 +957,43 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>938.24</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1079.55</v>
-      </c>
+        <v>50.4</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>30.00%</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
+          <t>25.60%</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1129억</t>
+          <t>5933억</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1012,7 +1002,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
@@ -1023,6 +1013,83 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>케이앤에스아이앤씨</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>통신 및 방송 장비 제조업</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>IBK투자증권</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>938.24</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1079.55</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>30.00%</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>11000</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,62 +613,52 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>니어스랩</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>무점포 소매업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>184.06</v>
-      </c>
-      <c r="H3" t="n">
-        <v>10.29</v>
-      </c>
+        <v>743.49</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.10%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>6.24%</t>
-        </is>
-      </c>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>36.93%</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>36.42%</t>
-        </is>
-      </c>
+          <t>37.19%</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1532억</t>
+          <t>2380억</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>7000</v>
+        <v>41200</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -690,79 +680,67 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>딜리셔스</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>무점포 소매업</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1146.41</v>
+        <v>184.06</v>
       </c>
       <c r="H4" t="n">
-        <v>1706.71</v>
+        <v>10.29</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>17.93%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.50%</t>
+          <t>6.24%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>41.03%</t>
+          <t>36.93%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>31.89%</t>
+          <t>36.42%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1579억</t>
+          <t>1532억</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>20700</v>
-      </c>
-      <c r="P4" t="n">
-        <v>30750</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>48.55%</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>22000</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-28.46%</t>
-        </is>
-      </c>
+        <v>7000</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
@@ -779,12 +757,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -794,38 +772,38 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1238</v>
+        <v>1146.41</v>
       </c>
       <c r="H5" t="n">
-        <v>1510.57</v>
+        <v>1706.71</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>17.93%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>74.17%</t>
+          <t>77.50%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>33.19%</t>
+          <t>41.03%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>24.86%</t>
+          <t>31.89%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1335억</t>
+          <t>1579억</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -834,22 +812,22 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>10000</v>
+        <v>20700</v>
       </c>
       <c r="P5" t="n">
-        <v>16560</v>
+        <v>30750</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>65.60%</t>
+          <t>48.55%</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>9400</v>
+        <v>22000</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-43.24%</t>
+          <t>-28.46%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -868,53 +846,53 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>714.52</v>
+        <v>1238</v>
       </c>
       <c r="H6" t="n">
-        <v>667.1799999999999</v>
+        <v>1510.57</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>6.92%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>34.58%</t>
+          <t>74.17%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>33.00%</t>
+          <t>33.19%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>24.41%</t>
+          <t>24.86%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1673억</t>
+          <t>1335억</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -923,22 +901,22 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>21500</v>
+        <v>10000</v>
       </c>
       <c r="P6" t="n">
-        <v>21500</v>
+        <v>16560</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>65.60%</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>14790</v>
+        <v>9400</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.21%</t>
+          <t>-43.24%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -957,43 +935,53 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>714.52</v>
+      </c>
+      <c r="H7" t="n">
+        <v>667.1799999999999</v>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>34.58%</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>25.60%</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>24.41%</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>5933억</t>
+          <t>1673억</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1002,12 +990,24 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+        <v>21500</v>
+      </c>
+      <c r="P7" t="n">
+        <v>21500</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>14790</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>-31.21%</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
@@ -1024,53 +1024,53 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>938.24</v>
+        <v>50.4</v>
       </c>
       <c r="H8" t="n">
-        <v>1079.55</v>
+        <v>3.09</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>71.42%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>30.00%</t>
+          <t>25.60%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>17.59%</t>
+          <t>25.36%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1129억</t>
+          <t>5933억</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -1090,6 +1090,150 @@
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>케이앤에스아이앤씨</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>통신 및 방송 장비 제조업</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>IBK투자증권</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>938.24</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1079.55</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>30.00%</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>11000</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>해치텍</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>DB증권</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>38.42%</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1269억</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>23000</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -567,7 +567,9 @@
       <c r="G2" t="n">
         <v>213.31</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>5.63</v>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>0.00%</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -636,7 +636,9 @@
       <c r="G3" t="n">
         <v>743.49</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>529.99</v>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1.26%</t>
@@ -739,10 +741,22 @@
       <c r="O4" t="n">
         <v>7000</v>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>-14.29%</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>5140</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-14.33%</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
@@ -1201,7 +1215,9 @@
       <c r="G10" t="n">
         <v>101.91</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>25.73</v>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>15.08%</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -568,20 +568,28 @@
         <v>213.31</v>
       </c>
       <c r="H2" t="n">
-        <v>5.63</v>
+        <v>5.51</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>66.92%</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>66.92%</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>1660억</t>
@@ -1174,10 +1182,22 @@
       <c r="O9" t="n">
         <v>11000</v>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>90.91%</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>15380</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>-26.76%</t>
+        </is>
+      </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -854,9 +854,21 @@
           <t>-28.46%</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>31000.0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>49.76%</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>51190.0</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -943,9 +955,21 @@
           <t>-43.24%</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>18740.0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>87.40%</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>69621.0</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -1198,9 +1222,21 @@
           <t>-26.76%</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -652,13 +652,21 @@
           <t>1.26%</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>39.42%</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>37.19%</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>32.49%</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>2380억</t>
@@ -1279,13 +1287,21 @@
           <t>15.08%</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>38.42%</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>1269억</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1137,10 +1137,22 @@
       <c r="O8" t="n">
         <v>12000</v>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>10960</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>-8.67%</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>17990</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>64.14%</t>
+        </is>
+      </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -603,10 +603,22 @@
       <c r="O2" t="n">
         <v>28400</v>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>28000</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>-1.41%</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>18580</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-33.64%</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,10 +692,22 @@
       <c r="O3" t="n">
         <v>41200</v>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>40500</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>-1.70%</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>28650</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>-29.26%</t>
+        </is>
+      </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
@@ -1003,53 +1015,43 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>714.52</v>
-      </c>
-      <c r="H7" t="n">
-        <v>667.1799999999999</v>
-      </c>
+        <v>63.41</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.91%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>34.58%</t>
-        </is>
-      </c>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>33.00%</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>24.41%</t>
-        </is>
-      </c>
+          <t>27.29%</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1673억</t>
+          <t>1874억</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1058,24 +1060,12 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>21500</v>
-      </c>
-      <c r="P7" t="n">
-        <v>21500</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
-        <v>14790</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>-31.21%</t>
-        </is>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
@@ -1092,53 +1082,53 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>50.4</v>
+        <v>714.52</v>
       </c>
       <c r="H8" t="n">
-        <v>3.09</v>
+        <v>667.1799999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>34.58%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>25.60%</t>
+          <t>33.00%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25.36%</t>
+          <t>24.41%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>5933억</t>
+          <t>1673억</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1147,22 +1137,22 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>12000</v>
+        <v>21500</v>
       </c>
       <c r="P8" t="n">
-        <v>10960</v>
+        <v>21500</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-8.67%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>17990</v>
+        <v>14790</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>64.14%</t>
+          <t>-31.21%</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1181,53 +1171,53 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>938.24</v>
+        <v>50.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1079.55</v>
+        <v>3.09</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>71.42%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>30.00%</t>
+          <t>25.60%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>17.59%</t>
+          <t>25.36%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1129억</t>
+          <t>5933억</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1236,39 +1226,27 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="P9" t="n">
-        <v>21000</v>
+        <v>10960</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>90.91%</t>
+          <t>-8.67%</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>15380</v>
+        <v>17990</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+          <t>64.14%</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1282,71 +1260,172 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>케이앤에스아이앤씨</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>통신 및 방송 장비 제조업</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>IBK투자증권</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>938.24</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1079.55</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>30.00%</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>11000</v>
+      </c>
+      <c r="P10" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>90.91%</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>15380</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>해치텍</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>반도체 제조업</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>DB증권</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="G11" t="n">
         <v>101.91</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H11" t="n">
         <v>25.73</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>15.08%</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>5.63%</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>38.42%</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>37.69%</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>1269억</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>무</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="O11" t="n">
         <v>23000</v>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1418,10 +1418,22 @@
       <c r="O11" t="n">
         <v>23000</v>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1036,7 +1036,9 @@
       <c r="G7" t="n">
         <v>63.41</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>2.85</v>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>0.17%</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1064,10 +1064,22 @@
       <c r="O7" t="n">
         <v>10000</v>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>8500</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>-15.00%</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>23500</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>176.47%</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,7 +635,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>니어스랩</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -645,69 +645,41 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>삼성증권</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>743.49</v>
-      </c>
-      <c r="H3" t="n">
-        <v>529.99</v>
-      </c>
+          <t>대신증권</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.26%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>39.42%</t>
-        </is>
-      </c>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.19%</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>32.49%</t>
-        </is>
-      </c>
+          <t>28.66%</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2380억</t>
+          <t>634억</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>41200</v>
-      </c>
-      <c r="P3" t="n">
-        <v>40500</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>-1.70%</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>28650</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>-29.26%</t>
-        </is>
-      </c>
+        <v>13800</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
@@ -724,77 +696,77 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>니어스랩</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>무점포 소매업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>184.06</v>
+        <v>743.49</v>
       </c>
       <c r="H4" t="n">
-        <v>10.29</v>
+        <v>529.99</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.24%</t>
+          <t>39.42%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>36.93%</t>
+          <t>37.19%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>36.42%</t>
+          <t>32.49%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1532억</t>
+          <t>2380억</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>7000</v>
+        <v>41200</v>
       </c>
       <c r="P4" t="n">
-        <v>6000</v>
+        <v>40500</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-14.29%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>5140</v>
+        <v>28650</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-14.33%</t>
+          <t>-29.26%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -813,94 +785,82 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>딜리셔스</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>무점포 소매업</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1146.41</v>
+        <v>184.06</v>
       </c>
       <c r="H5" t="n">
-        <v>1706.71</v>
+        <v>10.29</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>17.93%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.50%</t>
+          <t>6.24%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>41.03%</t>
+          <t>36.93%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>31.89%</t>
+          <t>36.42%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1579억</t>
+          <t>1532억</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>20700</v>
+        <v>7000</v>
       </c>
       <c r="P5" t="n">
-        <v>30750</v>
+        <v>6000</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>48.55%</t>
+          <t>-14.29%</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>22000</v>
+        <v>5140</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-28.46%</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>31000.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>49.76%</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>51190.0</t>
-        </is>
-      </c>
+          <t>-14.33%</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -914,12 +874,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -929,38 +889,38 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1238</v>
+        <v>1146.41</v>
       </c>
       <c r="H6" t="n">
-        <v>1510.57</v>
+        <v>1706.71</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>17.93%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.17%</t>
+          <t>77.50%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>33.19%</t>
+          <t>41.03%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>24.86%</t>
+          <t>31.89%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1335억</t>
+          <t>1579억</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -969,37 +929,37 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>10000</v>
+        <v>20700</v>
       </c>
       <c r="P6" t="n">
-        <v>16560</v>
+        <v>30750</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>65.60%</t>
+          <t>48.55%</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>9400</v>
+        <v>22000</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-43.24%</t>
+          <t>-28.46%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>18740.0</t>
+          <t>31000.0</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>87.40%</t>
+          <t>49.76%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>69621.0</t>
+          <t>51190.0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr"/>
@@ -1015,45 +975,53 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>63.41</v>
+        <v>1238</v>
       </c>
       <c r="H7" t="n">
-        <v>2.85</v>
+        <v>1510.57</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.17%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>6.92%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>74.17%</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>27.29%</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>33.19%</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>24.86%</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1874억</t>
+          <t>1335억</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1065,24 +1033,36 @@
         <v>10000</v>
       </c>
       <c r="P7" t="n">
-        <v>8500</v>
+        <v>16560</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-15.00%</t>
+          <t>65.60%</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>23500</v>
+        <v>9400</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>176.47%</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
+          <t>-43.24%</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>18740.0</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>87.40%</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>69621.0</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1096,53 +1076,45 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>714.52</v>
+        <v>63.41</v>
       </c>
       <c r="H8" t="n">
-        <v>667.1799999999999</v>
+        <v>2.85</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.91%</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>34.58%</t>
-        </is>
-      </c>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>33.00%</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>24.41%</t>
-        </is>
-      </c>
+          <t>27.29%</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1673억</t>
+          <t>1874억</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1151,22 +1123,22 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>21500</v>
+        <v>10000</v>
       </c>
       <c r="P8" t="n">
-        <v>21500</v>
+        <v>8500</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-15.00%</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>14790</v>
+        <v>23500</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-31.21%</t>
+          <t>176.47%</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1185,53 +1157,53 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>50.4</v>
+        <v>714.52</v>
       </c>
       <c r="H9" t="n">
-        <v>3.09</v>
+        <v>667.1799999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>34.58%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>25.60%</t>
+          <t>33.00%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>25.36%</t>
+          <t>24.41%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>5933억</t>
+          <t>1673억</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1240,22 +1212,22 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>12000</v>
+        <v>21500</v>
       </c>
       <c r="P9" t="n">
-        <v>10960</v>
+        <v>21500</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-8.67%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>17990</v>
+        <v>14790</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>64.14%</t>
+          <t>-31.21%</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1269,99 +1241,49 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>938.24</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>30.00%</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>11000</v>
-      </c>
-      <c r="P10" t="n">
-        <v>21000</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>90.91%</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>15380</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1375,53 +1297,53 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>101.91</v>
+        <v>50.4</v>
       </c>
       <c r="H11" t="n">
-        <v>25.73</v>
+        <v>3.09</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15.08%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.63%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>38.42%</t>
+          <t>25.60%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>37.69%</t>
+          <t>25.36%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1269억</t>
+          <t>5933억</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1430,22 +1352,22 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>23000</v>
+        <v>12000</v>
       </c>
       <c r="P11" t="n">
-        <v>20500</v>
+        <v>10960</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>-10.87%</t>
+          <t>-8.67%</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>13930</v>
+        <v>17990</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-32.05%</t>
+          <t>64.14%</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1453,6 +1375,294 @@
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>스펙</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>케이비제34호스팩</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>금융 지원 서비스업</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>KB증권</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>케이앤에스아이앤씨</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>통신 및 방송 장비 제조업</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>IBK투자증권</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>938.24</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1079.55</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>30.00%</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>11000</v>
+      </c>
+      <c r="P13" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>90.91%</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>15380</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>스펙</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>한국제17호스팩</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>금융 지원 서비스업</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>한국투자증권</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>해치텍</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DB증권</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="H15" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>38.42%</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1269억</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>23000</v>
+      </c>
+      <c r="P15" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1105,13 +1105,21 @@
           <t>0.17%</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10.93%</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>27.29%</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>26.42%</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>1874억</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -651,11 +651,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,10 +648,20 @@
           <t>대신증권</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>219.56</v>
+      </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8.98%</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
@@ -661,16 +671,16 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>634억</t>
+          <t>460억</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>13800</v>
+        <v>10000</v>
       </c>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -683,7 +693,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -692,7 +702,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>니어스랩</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -702,43 +712,33 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>743.49</v>
-      </c>
-      <c r="H4" t="n">
-        <v>529.99</v>
-      </c>
+        <v>219.56</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.26%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>39.42%</t>
-        </is>
-      </c>
+          <t>8.98%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>37.19%</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>32.49%</t>
-        </is>
-      </c>
+          <t>28.66%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2380억</t>
+          <t>460억</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -747,24 +747,12 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>41200</v>
-      </c>
-      <c r="P4" t="n">
-        <v>40500</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>-1.70%</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>28650</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-29.26%</t>
-        </is>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
@@ -772,7 +760,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -781,77 +769,77 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>니어스랩</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>무점포 소매업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>184.06</v>
+        <v>743.49</v>
       </c>
       <c r="H5" t="n">
-        <v>10.29</v>
+        <v>529.99</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.24%</t>
+          <t>39.42%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>36.93%</t>
+          <t>37.19%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>36.42%</t>
+          <t>32.49%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1532억</t>
+          <t>2380억</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>7000</v>
+        <v>41200</v>
       </c>
       <c r="P5" t="n">
-        <v>6000</v>
+        <v>40500</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-14.29%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>5140</v>
+        <v>28650</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-14.33%</t>
+          <t>-29.26%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -861,7 +849,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -870,99 +858,87 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>딜리셔스</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>무점포 소매업</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1146.41</v>
+        <v>184.06</v>
       </c>
       <c r="H6" t="n">
-        <v>1706.71</v>
+        <v>10.29</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>17.93%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.50%</t>
+          <t>6.24%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>41.03%</t>
+          <t>36.93%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>31.89%</t>
+          <t>36.42%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1579억</t>
+          <t>1532억</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>20700</v>
+        <v>7000</v>
       </c>
       <c r="P6" t="n">
-        <v>30750</v>
+        <v>6000</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>48.55%</t>
+          <t>-14.29%</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>22000</v>
+        <v>5140</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.46%</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>31000.0</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>49.76%</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>51190.0</t>
-        </is>
-      </c>
+          <t>-14.33%</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -971,12 +947,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -986,38 +962,38 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1238</v>
+        <v>1146.41</v>
       </c>
       <c r="H7" t="n">
-        <v>1510.57</v>
+        <v>1706.71</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>17.93%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>74.17%</t>
+          <t>77.50%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>33.19%</t>
+          <t>41.03%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24.86%</t>
+          <t>31.89%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1335억</t>
+          <t>1579억</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1026,44 +1002,44 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>10000</v>
+        <v>20700</v>
       </c>
       <c r="P7" t="n">
-        <v>16560</v>
+        <v>30750</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>65.60%</t>
+          <t>48.55%</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>9400</v>
+        <v>22000</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-43.24%</t>
+          <t>-28.46%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>18740.0</t>
+          <t>31000.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>87.40%</t>
+          <t>49.76%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>69621.0</t>
+          <t>51190.0</t>
         </is>
       </c>
       <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1072,53 +1048,53 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>63.41</v>
+        <v>1238</v>
       </c>
       <c r="H8" t="n">
-        <v>2.85</v>
+        <v>1510.57</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>6.92%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10.93%</t>
+          <t>74.17%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>27.29%</t>
+          <t>33.19%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>26.42%</t>
+          <t>24.86%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1874억</t>
+          <t>1335억</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1130,29 +1106,41 @@
         <v>10000</v>
       </c>
       <c r="P8" t="n">
-        <v>8500</v>
+        <v>16560</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-15.00%</t>
+          <t>65.60%</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>23500</v>
+        <v>9400</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>176.47%</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+          <t>-43.24%</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>18740.0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>87.40%</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>69621.0</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1161,53 +1149,53 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>714.52</v>
+        <v>63.41</v>
       </c>
       <c r="H9" t="n">
-        <v>667.1799999999999</v>
+        <v>2.85</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>34.58%</t>
+          <t>10.93%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>33.00%</t>
+          <t>27.29%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>24.41%</t>
+          <t>26.42%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1673억</t>
+          <t>1874억</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1216,22 +1204,22 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>21500</v>
+        <v>10000</v>
       </c>
       <c r="P9" t="n">
-        <v>21500</v>
+        <v>8500</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-15.00%</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>14790</v>
+        <v>23500</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-31.21%</t>
+          <t>176.47%</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1241,50 +1229,88 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>714.52</v>
+      </c>
       <c r="H10" t="n">
-        <v>357</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+        <v>667.1799999999999</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>34.58%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>24.41%</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1673억</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O10" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+        <v>21500</v>
+      </c>
+      <c r="P10" t="n">
+        <v>21500</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>14790</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-31.21%</t>
+        </is>
+      </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
@@ -1292,88 +1318,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>50.4</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>3.17%</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>25.60%</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>25.36%</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>5933억</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P11" t="n">
-        <v>10960</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>-8.67%</t>
-        </is>
-      </c>
-      <c r="R11" t="n">
-        <v>17990</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>64.14%</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
@@ -1381,48 +1369,88 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>25.60%</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>25.36%</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>5933억</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O12" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10960</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>-8.67%</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>17990</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>64.14%</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
@@ -1430,243 +1458,292 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>938.24</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>30.00%</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>11000</v>
-      </c>
-      <c r="P13" t="n">
-        <v>21000</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>90.91%</t>
-        </is>
-      </c>
-      <c r="R13" t="n">
-        <v>15380</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>938.24</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1079.55</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>30.00%</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O14" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+        <v>11000</v>
+      </c>
+      <c r="P14" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>90.91%</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>15380</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="H15" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>38.42%</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>1269억</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>23000</v>
-      </c>
-      <c r="P15" t="n">
-        <v>20500</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>-10.87%</t>
-        </is>
-      </c>
-      <c r="R15" t="n">
-        <v>13930</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>-32.05%</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>해치텍</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>DB증권</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="H16" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>38.42%</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1269억</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>23000</v>
+      </c>
+      <c r="P16" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,7 +693,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -702,7 +702,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>니어스랩</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -712,33 +712,43 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>219.56</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>743.49</v>
+      </c>
+      <c r="H4" t="n">
+        <v>529.99</v>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.98%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>39.42%</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>28.66%</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>37.19%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>32.49%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>460억</t>
+          <t>2380억</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -747,12 +757,24 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+        <v>41200</v>
+      </c>
+      <c r="P4" t="n">
+        <v>40500</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>-1.70%</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>28650</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-29.26%</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
@@ -760,7 +782,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -769,77 +791,77 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>니어스랩</t>
+          <t>딜리셔스</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>무점포 소매업</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>743.49</v>
+        <v>184.06</v>
       </c>
       <c r="H5" t="n">
-        <v>529.99</v>
+        <v>10.29</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>39.42%</t>
+          <t>6.24%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>37.19%</t>
+          <t>36.93%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>32.49%</t>
+          <t>36.42%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2380억</t>
+          <t>1532억</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>41200</v>
+        <v>7000</v>
       </c>
       <c r="P5" t="n">
-        <v>40500</v>
+        <v>6000</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-1.70%</t>
+          <t>-14.29%</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>28650</v>
+        <v>5140</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-29.26%</t>
+          <t>-14.33%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -849,7 +871,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -858,87 +880,99 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>무점포 소매업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>184.06</v>
+        <v>1146.41</v>
       </c>
       <c r="H6" t="n">
-        <v>10.29</v>
+        <v>1706.71</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>17.93%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.24%</t>
+          <t>77.50%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>36.93%</t>
+          <t>41.03%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>36.42%</t>
+          <t>31.89%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>1532억</t>
+          <t>1579억</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>7000</v>
+        <v>20700</v>
       </c>
       <c r="P6" t="n">
-        <v>6000</v>
+        <v>30750</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-14.29%</t>
+          <t>48.55%</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>5140</v>
+        <v>22000</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-14.33%</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+          <t>-28.46%</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>31000.0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>49.76%</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>51190.0</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -947,12 +981,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -962,38 +996,38 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1146.41</v>
+        <v>1238</v>
       </c>
       <c r="H7" t="n">
-        <v>1706.71</v>
+        <v>1510.57</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>17.93%</t>
+          <t>6.92%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.50%</t>
+          <t>74.17%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>41.03%</t>
+          <t>33.19%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>31.89%</t>
+          <t>24.86%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1579억</t>
+          <t>1335억</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1002,44 +1036,44 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>20700</v>
+        <v>10000</v>
       </c>
       <c r="P7" t="n">
-        <v>30750</v>
+        <v>16560</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>48.55%</t>
+          <t>65.60%</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>22000</v>
+        <v>9400</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.46%</t>
+          <t>-43.24%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>31000.0</t>
+          <t>18740.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>49.76%</t>
+          <t>87.40%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>51190.0</t>
+          <t>69621.0</t>
         </is>
       </c>
       <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1048,53 +1082,53 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1238</v>
+        <v>63.41</v>
       </c>
       <c r="H8" t="n">
-        <v>1510.57</v>
+        <v>2.85</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>74.17%</t>
+          <t>10.93%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>33.19%</t>
+          <t>27.29%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>24.86%</t>
+          <t>26.42%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1335억</t>
+          <t>1874억</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1106,41 +1140,29 @@
         <v>10000</v>
       </c>
       <c r="P8" t="n">
-        <v>16560</v>
+        <v>8500</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>65.60%</t>
+          <t>-15.00%</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>9400</v>
+        <v>23500</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-43.24%</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>18740.0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>87.40%</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>69621.0</t>
-        </is>
-      </c>
+          <t>176.47%</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1149,53 +1171,53 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>63.41</v>
+        <v>714.52</v>
       </c>
       <c r="H9" t="n">
-        <v>2.85</v>
+        <v>667.1799999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10.93%</t>
+          <t>34.58%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>27.29%</t>
+          <t>33.00%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>26.42%</t>
+          <t>24.41%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1874억</t>
+          <t>1673억</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1204,22 +1226,22 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>10000</v>
+        <v>21500</v>
       </c>
       <c r="P9" t="n">
-        <v>8500</v>
+        <v>21500</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-15.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>23500</v>
+        <v>14790</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>176.47%</t>
+          <t>-31.21%</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1229,88 +1251,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>714.52</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>667.1799999999999</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1.91%</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>34.58%</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>33.00%</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>24.41%</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1673억</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>21500</v>
-      </c>
-      <c r="P10" t="n">
-        <v>21500</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>14790</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>-31.21%</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
@@ -1318,50 +1302,88 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>50.4</v>
+      </c>
       <c r="H11" t="n">
-        <v>357</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+        <v>3.09</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>25.60%</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>25.36%</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>5933억</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10960</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>-8.67%</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>17990</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>64.14%</t>
+        </is>
+      </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
@@ -1369,88 +1391,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>3.17%</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>25.60%</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>25.36%</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>5933억</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P12" t="n">
-        <v>10960</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>-8.67%</t>
-        </is>
-      </c>
-      <c r="R12" t="n">
-        <v>17990</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>64.14%</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
@@ -1458,292 +1440,243 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>938.24</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1079.55</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>30.00%</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O13" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+        <v>11000</v>
+      </c>
+      <c r="P13" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>90.91%</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>15380</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>938.24</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>30.00%</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>11000</v>
-      </c>
-      <c r="P14" t="n">
-        <v>21000</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>90.91%</t>
-        </is>
-      </c>
-      <c r="R14" t="n">
-        <v>15380</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>DB증권</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="H15" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>38.42%</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1269억</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+        <v>23000</v>
+      </c>
+      <c r="P15" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>해치텍</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>반도체 제조업</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>DB증권</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="H16" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>38.42%</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>1269억</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>23000</v>
-      </c>
-      <c r="P16" t="n">
-        <v>20500</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>-10.87%</t>
-        </is>
-      </c>
-      <c r="R16" t="n">
-        <v>13930</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>-32.05%</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -671,7 +671,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>460억</t>
+          <t>1222억</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1874억</t>
+          <t>1876억</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>미래에셋증권, 삼성증권</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -568,7 +568,7 @@
         <v>213.31</v>
       </c>
       <c r="H2" t="n">
-        <v>5.51</v>
+        <v>5.63</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>714.52</v>
       </c>
       <c r="H9" t="n">
-        <v>667.1799999999999</v>
+        <v>666.78</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1291,10 +1291,22 @@
       <c r="O10" t="n">
         <v>2000</v>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>4000</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>2075</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-48.12%</t>
+        </is>
+      </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -656,7 +656,9 @@
       <c r="G3" t="n">
         <v>219.56</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>1047.78</v>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>8.98%</t>
@@ -1431,7 +1433,9 @@
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>397.33</v>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -1581,7 +1585,9 @@
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>494.62</v>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
